--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/pre LAM_HRM-2031-0172/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/pre LAM_HRM-2031-0172/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.0213</v>
+        <v>17.27069</v>
       </c>
       <c r="D2" t="n">
-        <v>16.83089</v>
+        <v>16.73773</v>
       </c>
       <c r="E2" t="n">
-        <v>16.63898</v>
+        <v>16.82744</v>
       </c>
       <c r="F2" t="n">
-        <v>42.82131</v>
+        <v>43.02288</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05112</v>
+        <v>0.05075</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8413</v>
+        <v>1.88834</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.11415</v>
+        <v>17.15115</v>
       </c>
       <c r="D3" t="n">
-        <v>17.00986</v>
+        <v>16.73562</v>
       </c>
       <c r="E3" t="n">
-        <v>16.78612</v>
+        <v>17.0352</v>
       </c>
       <c r="F3" t="n">
-        <v>42.05059</v>
+        <v>42.59748</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05079</v>
+        <v>0.05251</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8294</v>
+        <v>1.86264</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.12847</v>
+        <v>17.30105</v>
       </c>
       <c r="D4" t="n">
-        <v>16.48775</v>
+        <v>16.65389</v>
       </c>
       <c r="E4" t="n">
-        <v>16.99616</v>
+        <v>16.83622</v>
       </c>
       <c r="F4" t="n">
-        <v>43.51206</v>
+        <v>43.01127</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05257</v>
+        <v>0.05048</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83956</v>
+        <v>1.84758</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.029</v>
+        <v>16.9099</v>
       </c>
       <c r="D6" t="n">
-        <v>16.0383</v>
+        <v>16.1723</v>
       </c>
       <c r="E6" t="n">
-        <v>16.35618</v>
+        <v>16.43831</v>
       </c>
       <c r="F6" t="n">
-        <v>21.57288</v>
+        <v>21.98816</v>
       </c>
       <c r="G6" t="n">
-        <v>34.2781</v>
+        <v>33.92659</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.94052</v>
+        <v>16.98826</v>
       </c>
       <c r="D7" t="n">
-        <v>16.29064</v>
+        <v>16.14793</v>
       </c>
       <c r="E7" t="n">
-        <v>16.67702</v>
+        <v>16.86779</v>
       </c>
       <c r="F7" t="n">
-        <v>21.67349</v>
+        <v>22.41026</v>
       </c>
       <c r="G7" t="n">
-        <v>34.38886</v>
+        <v>35.20955</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.60901</v>
+        <v>16.73119</v>
       </c>
       <c r="D8" t="n">
-        <v>15.97667</v>
+        <v>16.051</v>
       </c>
       <c r="E8" t="n">
-        <v>16.59893</v>
+        <v>16.69715</v>
       </c>
       <c r="F8" t="n">
-        <v>21.81006</v>
+        <v>22.05898</v>
       </c>
       <c r="G8" t="n">
-        <v>33.964</v>
+        <v>34.69709</v>
       </c>
     </row>
   </sheetData>
